--- a/data/trans_dic/P25A$medico-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P25A$medico-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, el consejo médico</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, el consejo médico (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,7; 31,74</t>
+          <t>17,37; 31,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,3; 18,03</t>
+          <t>7,94; 17,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,95; 22,1</t>
+          <t>9,67; 22,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,19; 19,34</t>
+          <t>2,19; 18,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 12,75</t>
+          <t>1,37; 12,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 15,22</t>
+          <t>1,73; 13,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,57; 26,15</t>
+          <t>14,77; 26,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,24; 15,33</t>
+          <t>7,33; 14,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,72; 17,94</t>
+          <t>7,71; 17,66</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,4; 33,8</t>
+          <t>21,62; 34,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,43; 25,09</t>
+          <t>14,59; 25,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,43; 23,17</t>
+          <t>11,45; 23,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,39; 14,65</t>
+          <t>2,55; 14,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,19; 20,42</t>
+          <t>6,3; 19,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 10,82</t>
+          <t>1,1; 10,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,04; 26,89</t>
+          <t>16,95; 26,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,1; 21,93</t>
+          <t>13,29; 22,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,76; 17,63</t>
+          <t>8,9; 17,61</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,41; 31,43</t>
+          <t>16,51; 30,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20,54; 35,72</t>
+          <t>20,08; 34,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23,89; 40,41</t>
+          <t>23,53; 40,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,12</t>
+          <t>0,0; 18,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,07; 14,41</t>
+          <t>3,02; 14,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,02; 26,51</t>
+          <t>9,57; 26,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,78; 25,22</t>
+          <t>12,94; 24,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,94; 25,26</t>
+          <t>15,31; 25,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20,27; 33,25</t>
+          <t>20,67; 32,85</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,21; 38,83</t>
+          <t>25,23; 38,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,0; 26,48</t>
+          <t>15,02; 26,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,05; 21,83</t>
+          <t>11,69; 21,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,32; 19,86</t>
+          <t>6,61; 20,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,42; 16,1</t>
+          <t>5,31; 17,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,34; 14,89</t>
+          <t>4,32; 15,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,75; 30,39</t>
+          <t>20,54; 30,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,49; 21,26</t>
+          <t>12,74; 21,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,71; 17,75</t>
+          <t>9,64; 17,07</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>23,46; 30,66</t>
+          <t>23,79; 30,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,9; 22,57</t>
+          <t>16,95; 22,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,13; 22,83</t>
+          <t>16,24; 23,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,34; 13,31</t>
+          <t>5,14; 12,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,3; 12,19</t>
+          <t>6,25; 12,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,33; 12,48</t>
+          <t>6,17; 12,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,99; 24,54</t>
+          <t>19,02; 24,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,96; 18,48</t>
+          <t>14,13; 18,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,39; 18,38</t>
+          <t>13,44; 18,12</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, el consejo médico</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, el consejo médico (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>22913; 41076</t>
+          <t>22483; 40966</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15655; 34013</t>
+          <t>14971; 33407</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10582; 26119</t>
+          <t>11429; 26449</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>906; 7987</t>
+          <t>903; 7765</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>979; 9190</t>
+          <t>985; 9173</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>990; 8191</t>
+          <t>930; 7259</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24884; 44648</t>
+          <t>25218; 45974</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18888; 39973</t>
+          <t>19100; 38357</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13272; 30858</t>
+          <t>13267; 30378</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39980; 63151</t>
+          <t>40402; 64355</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35883; 62386</t>
+          <t>36281; 62845</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20252; 41071</t>
+          <t>20298; 41129</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1836; 11268</t>
+          <t>1960; 11140</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6082; 20082</t>
+          <t>6189; 19111</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>952; 9337</t>
+          <t>952; 9121</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44956; 70936</t>
+          <t>44702; 71137</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>45465; 76090</t>
+          <t>46115; 76900</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23099; 46481</t>
+          <t>23458; 46428</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>22035; 42206</t>
+          <t>22173; 41329</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>35405; 61573</t>
+          <t>34607; 59319</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31902; 53959</t>
+          <t>31426; 54282</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 7192</t>
+          <t>0; 7495</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3169; 14870</t>
+          <t>3119; 14773</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6726; 19764</t>
+          <t>7132; 20097</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23979; 43883</t>
+          <t>22513; 43060</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>41165; 69607</t>
+          <t>42188; 69996</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>42181; 69204</t>
+          <t>43005; 68364</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>43869; 67552</t>
+          <t>43900; 67750</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30951; 54639</t>
+          <t>31003; 55178</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19500; 38522</t>
+          <t>20628; 38787</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5865; 18434</t>
+          <t>6132; 19462</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4996; 18185</t>
+          <t>6005; 19551</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5254; 18038</t>
+          <t>5238; 18743</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>52688; 81094</t>
+          <t>54798; 82375</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>39895; 67892</t>
+          <t>40671; 67516</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28904; 52832</t>
+          <t>28694; 50786</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>146547; 191499</t>
+          <t>148595; 191333</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>137926; 184183</t>
+          <t>138297; 185369</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>97643; 138260</t>
+          <t>98347; 139481</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13395; 33379</t>
+          <t>12894; 30914</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>24372; 47132</t>
+          <t>24164; 47385</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21270; 41895</t>
+          <t>20725; 41942</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>166235; 214789</t>
+          <t>166517; 214680</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>167872; 222191</t>
+          <t>169939; 222787</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>125999; 173037</t>
+          <t>126555; 170583</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25A$medico-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P25A$medico-Habitat-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,37; 31,65</t>
+          <t>17,84; 32,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,94; 17,71</t>
+          <t>8,03; 18,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,67; 22,38</t>
+          <t>9,67; 22,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,19; 18,8</t>
+          <t>2,21; 19,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 12,73</t>
+          <t>1,38; 12,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,73; 13,49</t>
+          <t>0,0; 13,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,77; 26,93</t>
+          <t>14,65; 26,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,33; 14,71</t>
+          <t>7,02; 14,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,71; 17,66</t>
+          <t>7,7; 17,83</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,62; 34,44</t>
+          <t>21,87; 35,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,59; 25,27</t>
+          <t>14,81; 25,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,45; 23,2</t>
+          <t>11,72; 23,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,55; 14,48</t>
+          <t>2,44; 15,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,3; 19,44</t>
+          <t>6,46; 19,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 10,56</t>
+          <t>1,11; 10,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,95; 26,97</t>
+          <t>16,71; 26,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,29; 22,16</t>
+          <t>13,3; 21,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,9; 17,61</t>
+          <t>8,68; 17,12</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,51; 30,77</t>
+          <t>16,65; 31,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20,08; 34,42</t>
+          <t>20,76; 34,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23,53; 40,65</t>
+          <t>23,21; 40,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,89</t>
+          <t>0,0; 19,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,02; 14,32</t>
+          <t>2,94; 14,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,57; 26,95</t>
+          <t>9,95; 27,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,94; 24,75</t>
+          <t>13,47; 25,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,31; 25,4</t>
+          <t>14,96; 25,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20,67; 32,85</t>
+          <t>20,11; 32,29</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,23; 38,94</t>
+          <t>24,93; 39,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,02; 26,74</t>
+          <t>15,46; 27,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,69; 21,98</t>
+          <t>10,89; 21,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,61; 20,97</t>
+          <t>6,54; 19,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,31; 17,3</t>
+          <t>5,23; 16,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,32; 15,48</t>
+          <t>4,31; 14,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,54; 30,88</t>
+          <t>20,02; 30,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,74; 21,14</t>
+          <t>12,63; 21,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,64; 17,07</t>
+          <t>9,54; 17,49</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>23,79; 30,63</t>
+          <t>23,81; 30,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,95; 22,71</t>
+          <t>16,94; 22,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,24; 23,04</t>
+          <t>16,32; 22,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,14; 12,33</t>
+          <t>5,37; 12,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,25; 12,26</t>
+          <t>6,2; 12,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,17; 12,49</t>
+          <t>6,25; 12,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,02; 24,53</t>
+          <t>19,03; 24,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,13; 18,52</t>
+          <t>14,09; 18,41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,44; 18,12</t>
+          <t>13,34; 18,32</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>22483; 40966</t>
+          <t>23095; 41934</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14971; 33407</t>
+          <t>15140; 34233</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11429; 26449</t>
+          <t>11429; 26610</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>903; 7765</t>
+          <t>914; 7892</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>985; 9173</t>
+          <t>996; 9067</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>930; 7259</t>
+          <t>0; 7455</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25218; 45974</t>
+          <t>25016; 45618</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19100; 38357</t>
+          <t>18309; 38267</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13267; 30378</t>
+          <t>13253; 30662</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>40402; 64355</t>
+          <t>40857; 66263</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36281; 62845</t>
+          <t>36826; 63619</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20298; 41129</t>
+          <t>20767; 40972</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1960; 11140</t>
+          <t>1878; 11714</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6189; 19111</t>
+          <t>6351; 18909</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>952; 9121</t>
+          <t>962; 8814</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44702; 71137</t>
+          <t>44080; 70586</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>46115; 76900</t>
+          <t>46166; 76271</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23458; 46428</t>
+          <t>22890; 45121</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>22173; 41329</t>
+          <t>22359; 41706</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>34607; 59319</t>
+          <t>35774; 60006</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31426; 54282</t>
+          <t>30989; 54243</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 7495</t>
+          <t>0; 7747</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3119; 14773</t>
+          <t>3031; 15202</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7132; 20097</t>
+          <t>7421; 20276</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22513; 43060</t>
+          <t>23443; 43577</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>42188; 69996</t>
+          <t>41224; 69167</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>43005; 68364</t>
+          <t>41853; 67200</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>43900; 67750</t>
+          <t>43376; 69124</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>31003; 55178</t>
+          <t>31914; 55839</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20628; 38787</t>
+          <t>19225; 37325</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6132; 19462</t>
+          <t>6066; 18355</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6005; 19551</t>
+          <t>5906; 18871</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5238; 18743</t>
+          <t>5224; 18085</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>54798; 82375</t>
+          <t>53415; 81230</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>40671; 67516</t>
+          <t>40326; 68223</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28694; 50786</t>
+          <t>28404; 52038</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>148595; 191333</t>
+          <t>148718; 190845</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>138297; 185369</t>
+          <t>138274; 185072</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>98347; 139481</t>
+          <t>98799; 136657</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12894; 30914</t>
+          <t>13457; 31506</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>24164; 47385</t>
+          <t>23978; 46866</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20725; 41942</t>
+          <t>20976; 41737</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>166517; 214680</t>
+          <t>166531; 214916</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>169939; 222787</t>
+          <t>169436; 221388</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>126555; 170583</t>
+          <t>125552; 172434</t>
         </is>
       </c>
     </row>
